--- a/data/trending_integrated_20261008_11.xlsx
+++ b/data/trending_integrated_20261008_11.xlsx
@@ -584,7 +584,7 @@
         <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30467371890</v>
+        <v>30559523130</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14150</v>
+        <v>13900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.02%</t>
+          <t>'+15.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>35570266420</v>
+        <v>36420836670</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11450</v>
+        <v>11310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.89%</t>
+          <t>'+14.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>46100917350</v>
+        <v>47287347525</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38750</v>
+        <v>14160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.04%</t>
+          <t>'+12.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="H5" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K5" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L5" t="n">
-        <v>39850</v>
+        <v>14190</v>
       </c>
       <c r="M5" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N5" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>94477406125</v>
+        <v>58578508090</v>
       </c>
       <c r="P5" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q5" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R5" t="n">
-        <v>199000</v>
+        <v>-324000</v>
       </c>
       <c r="S5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
+          <t>유증 물량 소화 완료 및 비만치료제 개발 기대감. HLB 그룹주 동반 상승 가능성과 함께 목표 주가 3만원 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '매수세']</t>
+          <t>['유상증자', '비만치료제', 'HLB 그룹주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6820</v>
+        <v>38550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.57%</t>
+          <t>'+6.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>18833739340</v>
+        <v>96948624050</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>199000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['기관', '외국인', '매수세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13200</v>
+        <v>6830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.01%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
         <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>6460</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>6930</v>
       </c>
       <c r="L7" t="n">
-        <v>14070</v>
+        <v>8390</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>50689510565</v>
+        <v>18980692400</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>9680</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>371</v>
       </c>
       <c r="R7" t="n">
-        <v>-324000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유증 물량 소화 완료 및 비만치료제 개발 기대감. HLB 그룹주 동반 상승 가능성과 함께 목표 주가 3만원 제시.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유상증자', '비만치료제', 'HLB 그룹주']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4545</v>
+        <v>4565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+3.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H8" t="n">
         <v>4.46</v>
@@ -1162,7 +1162,7 @@
         <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>67771131451</v>
+        <v>70590080038</v>
       </c>
       <c r="P8" t="n">
         <v>5470</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1755000</v>
+        <v>1745000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G9" t="n">
-        <v>1836</v>
+        <v>1798</v>
       </c>
       <c r="H9" t="n">
         <v>49.59</v>
@@ -1254,7 +1254,7 @@
         <v>49.71</v>
       </c>
       <c r="O9" t="n">
-        <v>1799795851500</v>
+        <v>1886564686000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>마이크론 주가 급등 및 2028년까지 반도체 부족 전망 뉴스. 일부 솔리다임 관련 악재에도 불구하고 반등 기대감 형성.</t>
+          <t>2028년 메모리 반도체 공급 부족 전망. 마이크론 주가 급등에 따른 SK하이닉스 주가 상승 기대감. 솔리다임 관련 주주 가치 훼손 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['마이크론', '반도체 부족', 'ADR']</t>
+          <t>['메모리반도체', '공급부족', '마이크론']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8260</v>
+        <v>46350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>186</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="G10" t="n">
-        <v>118</v>
+        <v>663</v>
       </c>
       <c r="H10" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>9667019765</v>
+        <v>20802264350</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-6000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>리보세라닙 병용요법 허가 가능성 및 글로벌 3상 진행. 공매도 세력과의 갈등 및 주가 상승 기대감. 우상향 차트와 함께 바이오 섹터 강세 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['리보세라닙', '공매도', '우상향']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45900</v>
+        <v>8260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>627</v>
+        <v>126</v>
       </c>
       <c r="H11" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K11" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L11" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M11" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N11" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>18818750225</v>
+        <v>10013965920</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R11" t="n">
-        <v>-12000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용 요법 허가와 긍정적인 임상 결과에 대한 기대감이 높으며, 공매도 세력과의 대립 구도 속에서 우상향 추세를 전망하는 의견이 지배적임.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '병용 요법', '공매도']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>268500</v>
+        <v>267000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G12" t="n">
-        <v>1979</v>
+        <v>1859</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>1618075438750</v>
+        <v>1732644467000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 108조원이라는 역대급 영업이익에도 불구하고 주가 하락이 이어지자, 특정 정치 세력의 경제 정책 실패를 원인으로 지목하며 강한 불만을 표출함.</t>
+          <t>100조 영업이익에도 불구하고 주가 하락. 정치적 요인 및 시장 시스템 붕괴에 대한 비난. 외국인, 기관의 행태에 대한 의구심.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '정치 정책']</t>
+          <t>['영업이익', '주가하락', '시장시스템']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>236000</v>
+        <v>237000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.65</v>
       </c>
       <c r="E13" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="H13" t="n">
         <v>3.47</v>
@@ -1613,7 +1613,7 @@
         <v>227000</v>
       </c>
       <c r="L13" t="n">
-        <v>236500</v>
+        <v>239500</v>
       </c>
       <c r="M13" t="n">
         <v>210500</v>
@@ -1622,7 +1622,7 @@
         <v>4.12</v>
       </c>
       <c r="O13" t="n">
-        <v>29510627000</v>
+        <v>31249756000</v>
       </c>
       <c r="P13" t="n">
         <v>1233000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19060</v>
+        <v>19050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.46%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1708,13 +1708,13 @@
         <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>19050</v>
+        <v>19040</v>
       </c>
       <c r="N14" t="n">
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>23096415520</v>
+        <v>24802557075</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16820</v>
+        <v>16800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>23672193720</v>
+        <v>24605216020</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1872,7 +1872,7 @@
         <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
         <v>10.02</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>38059478100</v>
+        <v>39307810150</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76700</v>
+        <v>55200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F17" t="n">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G17" t="n">
-        <v>672</v>
+        <v>469</v>
       </c>
       <c r="H17" t="n">
-        <v>22.49</v>
+        <v>1.32</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>80500</v>
+        <v>58100</v>
       </c>
       <c r="K17" t="n">
-        <v>79600</v>
+        <v>63200</v>
       </c>
       <c r="L17" t="n">
-        <v>79600</v>
+        <v>63800</v>
       </c>
       <c r="M17" t="n">
-        <v>76300</v>
+        <v>53100</v>
       </c>
       <c r="N17" t="n">
-        <v>22.59</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>115441926800</v>
+        <v>46036453650</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>63800</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>25600</v>
       </c>
       <c r="R17" t="n">
-        <v>-360000</v>
+        <v>-170000</v>
       </c>
       <c r="S17" t="n">
-        <v>-54000</v>
+        <v>-21000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스 발전 사업 확정 소식에도 불구하고 주가가 큰 폭으로 하락하며 실망감과 분노를 표출함. 원전 관련 기대감은 하락 요인으로 작용.</t>
+          <t>국내 시장 석권 준비 및 비만주 급등 관련 기대감. 주가 조작 및 차명거래 의혹 제기. 공매도 지속 및 급락에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['가스 발전', '주가 하락', '원전']</t>
+          <t>['비만주', '주가조작', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17060</v>
+        <v>16990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-5.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>64658037770</v>
+        <v>67101153225</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 급락의 영향으로 국내 주가도 하락세를 보이며, 일부 투자자는 매도를 고려하고 있으나 반등을 기대하는 의견도 존재함. 외인 매도세가 부담.</t>
+          <t>미국 광통신 주가 급락에 따른 국내 주가 하락 우려. 외국인 매도세 지속 및 프로그램 매매 불안정성. 주가 반등에 대한 기대와 함께 매도 의견 공존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '주가 하락', '외인 매도']</t>
+          <t>['광통신', '주가하락', '외국인매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4930</v>
+        <v>76200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="G19" t="n">
-        <v>252</v>
+        <v>733</v>
       </c>
       <c r="H19" t="n">
-        <v>4.65</v>
+        <v>22.49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5210</v>
+        <v>80500</v>
       </c>
       <c r="K19" t="n">
-        <v>5220</v>
+        <v>79600</v>
       </c>
       <c r="L19" t="n">
-        <v>5310</v>
+        <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>4755</v>
+        <v>76100</v>
       </c>
       <c r="N19" t="n">
-        <v>4.72</v>
+        <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>56077416530</v>
+        <v>122771430650</v>
       </c>
       <c r="P19" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-152000</v>
+        <v>-360000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>30억 규모의 CB 발행 및 기타 법인의 대규모 장내 매도로 인해 주가 급락이 예상되며, 투자자들에게 주의를 당부하고 있으나 일부에서는 급등을 기대하는 의견도 존재함.</t>
+          <t>미국 텍사스 가스 발전 확정 소식에도 불구하고 주가 하락. 원전 수출 기대감과 공매도 세력에 대한 불만 표출. 주가 하락 이유에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['CB 발행', '장내 매도', '악재']</t>
+          <t>['가스발전', '원전수출', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7330</v>
+        <v>4865</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.27%</t>
+          <t>'-6.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>355</v>
+        <v>258</v>
       </c>
       <c r="H20" t="n">
-        <v>3.09</v>
+        <v>4.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7820</v>
+        <v>5210</v>
       </c>
       <c r="K20" t="n">
-        <v>8080</v>
+        <v>5220</v>
       </c>
       <c r="L20" t="n">
-        <v>8510</v>
+        <v>5310</v>
       </c>
       <c r="M20" t="n">
-        <v>7170</v>
+        <v>4755</v>
       </c>
       <c r="N20" t="n">
-        <v>5.12</v>
+        <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>75999188940</v>
+        <v>57509167740</v>
       </c>
       <c r="P20" t="n">
-        <v>23500</v>
+        <v>8100</v>
       </c>
       <c r="Q20" t="n">
-        <v>2890</v>
+        <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-501000</v>
+        <v>-152000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 급락 및 공매도에 대한 비판. 성수동 부동산 개발 관련 기대감도 있으나, 전반적으로 부정적 전망 우세.</t>
+          <t>주가 급등 기대감 속 전환사채 발행 및 장내매도 악재 발생. 30억 규모 발행 자금 사용처에 대한 의문. 단기 급등 후 대규모 매도 물량 출회 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 급락', '공매도', '부동산 개발']</t>
+          <t>['전환사채', '장내매도', '악재']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>54200</v>
+        <v>7270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.71%</t>
+          <t>'-7.03%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.02</v>
+        <v>-2.03</v>
       </c>
       <c r="E21" t="n">
-        <v>241</v>
+        <v>135</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>456</v>
+        <v>363</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>58100</v>
+        <v>7820</v>
       </c>
       <c r="K21" t="n">
-        <v>63200</v>
+        <v>8080</v>
       </c>
       <c r="L21" t="n">
-        <v>63800</v>
+        <v>8510</v>
       </c>
       <c r="M21" t="n">
-        <v>53100</v>
+        <v>7170</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3</v>
+        <v>5.12</v>
       </c>
       <c r="O21" t="n">
-        <v>44862716250</v>
+        <v>76354132650</v>
       </c>
       <c r="P21" t="n">
-        <v>63800</v>
+        <v>23500</v>
       </c>
       <c r="Q21" t="n">
-        <v>25600</v>
+        <v>2890</v>
       </c>
       <c r="R21" t="n">
-        <v>-170000</v>
+        <v>-501000</v>
       </c>
       <c r="S21" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>국내 시장 석권 준비라는 긍정적 전망에도 불구하고, 급격한 주가 하락으로 투자자들의 불만이 고조되고 있음. 주가 조작 및 공매도에 대한 신고 의지가 강함.</t>
+          <t>주가 급락 및 공매도에 대한 비판. 성수동 부동산 개발 관련 기대감도 있으나, 전반적으로 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['신약 개발', '주가 하락', '공매도']</t>
+          <t>['주가 급락', '공매도', '부동산 개발']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15260</v>
+        <v>15180</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.68%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>29160857880</v>
+        <v>29479978150</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9830</v>
+        <v>9850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.54%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>5604159010</v>
+        <v>5695923050</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_11.xlsx
+++ b/data/trending_integrated_20261008_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30559523130</v>
+        <v>30629071950</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13900</v>
+        <v>13830</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.93%</t>
+          <t>'+15.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>36420836670</v>
+        <v>37176391530</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11310</v>
+        <v>11280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.47%</t>
+          <t>'+14.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>47287347525</v>
+        <v>48212332290</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14160</v>
+        <v>13670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.65%</t>
+          <t>'+8.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H5" t="n">
         <v>1.07</v>
@@ -877,7 +877,7 @@
         <v>12970</v>
       </c>
       <c r="L5" t="n">
-        <v>14190</v>
+        <v>14200</v>
       </c>
       <c r="M5" t="n">
         <v>12500</v>
@@ -886,7 +886,7 @@
         <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>58578508090</v>
+        <v>66475352610</v>
       </c>
       <c r="P5" t="n">
         <v>22250</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38550</v>
+        <v>6940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.49%</t>
+          <t>'+7.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>96948624050</v>
+        <v>19295919920</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R6" t="n">
-        <v>199000</v>
+        <v>-25000</v>
       </c>
       <c r="S6" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '매수세']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6830</v>
+        <v>38750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.73%</t>
+          <t>'+7.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>18980692400</v>
+        <v>99649918000</v>
       </c>
       <c r="P7" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-25000</v>
+        <v>199000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['기관', '외국인', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4565</v>
+        <v>4570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.05%</t>
+          <t>'+3.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="H8" t="n">
         <v>4.46</v>
@@ -1162,7 +1162,7 @@
         <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>70590080038</v>
+        <v>73664758948</v>
       </c>
       <c r="P8" t="n">
         <v>5470</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1745000</v>
+        <v>1746500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G9" t="n">
-        <v>1798</v>
+        <v>1769</v>
       </c>
       <c r="H9" t="n">
         <v>49.59</v>
@@ -1254,7 +1254,7 @@
         <v>49.71</v>
       </c>
       <c r="O9" t="n">
-        <v>1886564686000</v>
+        <v>1982945539500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2028년 메모리 반도체 공급 부족 전망. 마이크론 주가 급등에 따른 SK하이닉스 주가 상승 기대감. 솔리다임 관련 주주 가치 훼손 우려.</t>
+          <t>28년 공급 부족 전망 및 마이크론 주가 상승에 따른 기대감. 솔리다임 상장 관련 주주 가치 훼손 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['메모리반도체', '공급부족', '마이크론']</t>
+          <t>['공급 부족', '마이크론', '솔리다임']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46350</v>
+        <v>8270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>663</v>
+        <v>132</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>20802264350</v>
+        <v>10394841520</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-6000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 가능성 및 글로벌 3상 진행. 공매도 세력과의 갈등 및 주가 상승 기대감. 우상향 차트와 함께 바이오 섹터 강세 전망.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '우상향']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8260</v>
+        <v>46000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="G11" t="n">
-        <v>126</v>
+        <v>717</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>10013965920</v>
+        <v>23407962975</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>-12000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력에 대한 압박. 우상향 차트 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['리보세라닙', '공매도', '우상향 차트']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>267000</v>
+        <v>267250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="G12" t="n">
-        <v>1859</v>
+        <v>1831</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>1732644467000</v>
+        <v>1821982816250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>100조 영업이익에도 불구하고 주가 하락. 정치적 요인 및 시장 시스템 붕괴에 대한 비난. 외국인, 기관의 행태에 대한 의구심.</t>
+          <t>막대한 영업이익에도 불구하고 주가 하락 지속. 정치적 요인 및 시장 시스템 붕괴에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가하락', '시장시스템']</t>
+          <t>['영업이익', '주가 하락', '정치적 요인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,123 +1575,123 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>237000</v>
+        <v>18985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-2.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>567</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
-        <v>3.47</v>
+        <v>27.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>241000</v>
+        <v>19540</v>
       </c>
       <c r="K13" t="n">
-        <v>227000</v>
+        <v>19490</v>
       </c>
       <c r="L13" t="n">
-        <v>239500</v>
+        <v>19500</v>
       </c>
       <c r="M13" t="n">
-        <v>210500</v>
+        <v>18950</v>
       </c>
       <c r="N13" t="n">
-        <v>4.12</v>
+        <v>27.67</v>
       </c>
       <c r="O13" t="n">
-        <v>31249756000</v>
+        <v>28972424480</v>
       </c>
       <c r="P13" t="n">
-        <v>1233000</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>120000</v>
+        <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>5000</v>
+        <v>-255000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-24000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 속 릴레이 계약 공시 기대감. 연기금 7일째 매수세 유입 및 바이오 섹터 내 경쟁력 부각.</t>
+          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '연기금']</t>
+          <t>['주가 하락', '신저가', '애널리스트']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19050</v>
+        <v>16840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-2.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>213</v>
+        <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19540</v>
+        <v>17340</v>
       </c>
       <c r="K14" t="n">
-        <v>19490</v>
+        <v>17190</v>
       </c>
       <c r="L14" t="n">
-        <v>19500</v>
+        <v>17220</v>
       </c>
       <c r="M14" t="n">
-        <v>19040</v>
+        <v>16710</v>
       </c>
       <c r="N14" t="n">
-        <v>27.67</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>24802557075</v>
+        <v>26006418310</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-255000</v>
+        <v>70000</v>
       </c>
       <c r="S14" t="n">
-        <v>-24000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
+          <t>공매도 및 대차 거래에 대한 우려와 주가 하락에 대한 불만. 주주들의 호소와 행동 촉구.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '신저가', '애널리스트']</t>
+          <t>['공매도', '대차 거래', '주주 호소']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16800</v>
+        <v>233500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1771,80 +1771,80 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>-0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>338</v>
+        <v>592</v>
       </c>
       <c r="H15" t="n">
-        <v>9.460000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17340</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>17190</v>
+        <v>227000</v>
       </c>
       <c r="L15" t="n">
-        <v>17220</v>
+        <v>239500</v>
       </c>
       <c r="M15" t="n">
-        <v>16710</v>
+        <v>210500</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="O15" t="n">
-        <v>24605216020</v>
+        <v>32302345750</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>70000</v>
+        <v>5000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 및 대차 거래에 대한 우려와 주가 하락에 대한 불만. 주주들의 호소와 행동 촉구.</t>
+          <t>공매도 과열 지정 및 연기금 7일 연속 매수. 릴레이 계약 공시 기대감 속 공매도 악마 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '대차 거래', '주주 호소']</t>
+          <t>['공매도', '연기금', '계약 공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28600</v>
+        <v>28550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-4.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H16" t="n">
         <v>10.02</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>39307810150</v>
+        <v>42093578625</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55200</v>
+        <v>16980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>469</v>
+        <v>362</v>
       </c>
       <c r="H17" t="n">
-        <v>1.32</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>58100</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>63200</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>63800</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>53100</v>
+        <v>16900</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>46036453650</v>
+        <v>68849047945</v>
       </c>
       <c r="P17" t="n">
-        <v>63800</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>25600</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-170000</v>
+        <v>-168000</v>
       </c>
       <c r="S17" t="n">
-        <v>-21000</v>
+        <v>-15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국내 시장 석권 준비 및 비만주 급등 관련 기대감. 주가 조작 및 차명거래 의혹 제기. 공매도 지속 및 급락에 대한 불만 토로.</t>
+          <t>미국 광통신주 급락에 따른 한국 시장 영향 우려. 주가 하락 및 외인 매도에 대한 불안감 증폭.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['비만주', '주가조작', '공매도']</t>
+          <t>['광통신', '주가 하락', '외인 매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16990</v>
+        <v>54900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.95</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
-        <v>338</v>
+        <v>486</v>
       </c>
       <c r="H18" t="n">
-        <v>3.97</v>
+        <v>1.32</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17940</v>
+        <v>58100</v>
       </c>
       <c r="K18" t="n">
-        <v>17770</v>
+        <v>63200</v>
       </c>
       <c r="L18" t="n">
-        <v>17940</v>
+        <v>63800</v>
       </c>
       <c r="M18" t="n">
-        <v>16900</v>
+        <v>53100</v>
       </c>
       <c r="N18" t="n">
-        <v>4.92</v>
+        <v>1.3</v>
       </c>
       <c r="O18" t="n">
-        <v>67101153225</v>
+        <v>46751931250</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>63800</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>25600</v>
       </c>
       <c r="R18" t="n">
-        <v>-168000</v>
+        <v>-170000</v>
       </c>
       <c r="S18" t="n">
-        <v>-15000</v>
+        <v>-21000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 급락에 따른 국내 주가 하락 우려. 외국인 매도세 지속 및 프로그램 매매 불안정성. 주가 반등에 대한 기대와 함께 매도 의견 공존.</t>
+          <t>신약 허가 및 판매 호조에도 불구하고 주가 급락. 차명거래 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '주가하락', '외국인매도']</t>
+          <t>['신약 허가', '주가 급락', '주가 조작']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76200</v>
+        <v>76050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-5.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F19" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G19" t="n">
-        <v>733</v>
+        <v>792</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2168,13 +2168,13 @@
         <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>76100</v>
+        <v>75700</v>
       </c>
       <c r="N19" t="n">
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>122771430650</v>
+        <v>141354289050</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스 발전 확정 소식에도 불구하고 주가 하락. 원전 수출 기대감과 공매도 세력에 대한 불만 표출. 주가 하락 이유에 대한 의문 제기.</t>
+          <t>미국 가스 발전 확정 소식 속 원전 관련 부정적 전망. 공매도와 당국의 미흡한 대응에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전수출', '공매도']</t>
+          <t>['가스 발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4865</v>
+        <v>4855</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.62%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>57509167740</v>
+        <v>58592989372</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 급등 기대감 속 전환사채 발행 및 장내매도 악재 발생. 30억 규모 발행 자금 사용처에 대한 의문. 단기 급등 후 대규모 매도 물량 출회 우려.</t>
+          <t>전환사채 및 기타법인 대량 매도 악재 발생. 초대형 악재 속 주가 급락 및 투자자 경고.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '장내매도', '악재']</t>
+          <t>['전환사채', '대량 매도', '악재']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7270</v>
+        <v>7240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.03%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-2.03</v>
       </c>
       <c r="E21" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H21" t="n">
         <v>3.09</v>
@@ -2358,7 +2358,7 @@
         <v>5.12</v>
       </c>
       <c r="O21" t="n">
-        <v>76354132650</v>
+        <v>76883719735</v>
       </c>
       <c r="P21" t="n">
         <v>23500</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15180</v>
+        <v>15240</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.16%</t>
+          <t>'-8.80%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>29479978150</v>
+        <v>29786085000</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2499,18 +2499,18 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9850</v>
+        <v>9980</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.54%</t>
+          <t>'-9.36%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
         <v>55</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>5695923050</v>
+        <v>5902258540</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_11.xlsx
+++ b/data/trending_integrated_20261008_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30629071950</v>
+        <v>30679072390</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13830</v>
+        <v>14100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.35%</t>
+          <t>'+17.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>37176391530</v>
+        <v>37783725365</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11280</v>
+        <v>11300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.17%</t>
+          <t>'+14.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>48212332290</v>
+        <v>48832725445</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13670</v>
+        <v>13650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.75%</t>
+          <t>'+8.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H5" t="n">
         <v>1.07</v>
@@ -886,7 +886,7 @@
         <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>66475352610</v>
+        <v>70249511405</v>
       </c>
       <c r="P5" t="n">
         <v>22250</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유증 물량 소화 완료 및 비만치료제 개발 기대감. HLB 그룹주 동반 상승 가능성과 함께 목표 주가 3만원 제시.</t>
+          <t>유증 물량 정리 및 바이오 관련 기대감. 1차 목표가 3만원 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유상증자', '비만치료제', 'HLB 그룹주']</t>
+          <t>['유증', '바이오', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6940</v>
+        <v>6900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.43%</t>
+          <t>'+6.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>19295919920</v>
+        <v>19424509860</v>
       </c>
       <c r="P6" t="n">
         <v>9680</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38750</v>
+        <v>38600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.04%</t>
+          <t>'+6.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H7" t="n">
         <v>31.86</v>
@@ -1070,7 +1070,7 @@
         <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>99649918000</v>
+        <v>101105677325</v>
       </c>
       <c r="P7" t="n">
         <v>45000</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4570</v>
+        <v>4495</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.16%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
         <v>142</v>
@@ -1162,7 +1162,7 @@
         <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>73664758948</v>
+        <v>76260761607</v>
       </c>
       <c r="P8" t="n">
         <v>5470</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1746500</v>
+        <v>1745500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+1.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G9" t="n">
-        <v>1769</v>
+        <v>1583</v>
       </c>
       <c r="H9" t="n">
         <v>49.59</v>
@@ -1254,7 +1254,7 @@
         <v>49.71</v>
       </c>
       <c r="O9" t="n">
-        <v>1982945539500</v>
+        <v>2043934886500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>28년 공급 부족 전망 및 마이크론 주가 상승에 따른 기대감. 솔리다임 상장 관련 주주 가치 훼손 우려.</t>
+          <t>솔리다임 상장 관련 논란. 마이크론 급등 및 삼성전자 실적 발표에 따른 영향 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공급 부족', '마이크론', '솔리다임']</t>
+          <t>['솔리다임', '마이크론', '실적 발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8270</v>
+        <v>8280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>10394841520</v>
+        <v>10639298980</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46000</v>
+        <v>45900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="F11" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>717</v>
+        <v>755</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>23407962975</v>
+        <v>24282898550</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력에 대한 압박. 우상향 차트 기반 긍정적 전망.</t>
+          <t>리보세라닙 병용요법 허가 및 글로벌 3상 종료 약물 관련 긍정적 전망. 공매도 압박.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '우상향 차트']</t>
+          <t>['리보세라닙', '3상 임상', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>267250</v>
+        <v>266750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G12" t="n">
-        <v>1831</v>
+        <v>1821</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>1821982816250</v>
+        <v>1893876816500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>막대한 영업이익에도 불구하고 주가 하락 지속. 정치적 요인 및 시장 시스템 붕괴에 대한 불만 표출.</t>
+          <t>영업이익 107조에도 주가 부양 실패. 정치적 책임론 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '정치적 요인']</t>
+          <t>['영업이익', '주가 부양', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,123 +1575,123 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18985</v>
+        <v>234000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.65</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>605</v>
       </c>
       <c r="H13" t="n">
-        <v>27.68</v>
+        <v>3.47</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19540</v>
+        <v>241000</v>
       </c>
       <c r="K13" t="n">
-        <v>19490</v>
+        <v>227000</v>
       </c>
       <c r="L13" t="n">
-        <v>19500</v>
+        <v>239500</v>
       </c>
       <c r="M13" t="n">
-        <v>18950</v>
+        <v>210500</v>
       </c>
       <c r="N13" t="n">
-        <v>27.67</v>
+        <v>4.12</v>
       </c>
       <c r="O13" t="n">
-        <v>28972424480</v>
+        <v>32841520250</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>1233000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18440</v>
+        <v>120000</v>
       </c>
       <c r="R13" t="n">
-        <v>-255000</v>
+        <v>5000</v>
       </c>
       <c r="S13" t="n">
-        <v>-24000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
+          <t>아일리아 영업이익 및 릴레이 계약 공시. 공매도 금지 및 연기금 매수 동향.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 하락', '신저가', '애널리스트']</t>
+          <t>['아일리아', '계약 공시', '공매도 금지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16840</v>
+        <v>18970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'-2.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>350</v>
+        <v>223</v>
       </c>
       <c r="H14" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17340</v>
+        <v>19540</v>
       </c>
       <c r="K14" t="n">
-        <v>17190</v>
+        <v>19490</v>
       </c>
       <c r="L14" t="n">
-        <v>17220</v>
+        <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>16710</v>
+        <v>18950</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>26006418310</v>
+        <v>29687693930</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>70000</v>
+        <v>-255000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-24000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 및 대차 거래에 대한 우려와 주가 하락에 대한 불만. 주주들의 호소와 행동 촉구.</t>
+          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차 거래', '주주 호소']</t>
+          <t>['주가 하락', '신저가', '애널리스트']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>233500</v>
+        <v>16800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1771,80 +1771,80 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.65</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>592</v>
+        <v>357</v>
       </c>
       <c r="H15" t="n">
-        <v>3.47</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>241000</v>
+        <v>17340</v>
       </c>
       <c r="K15" t="n">
-        <v>227000</v>
+        <v>17190</v>
       </c>
       <c r="L15" t="n">
-        <v>239500</v>
+        <v>17220</v>
       </c>
       <c r="M15" t="n">
-        <v>210500</v>
+        <v>16710</v>
       </c>
       <c r="N15" t="n">
-        <v>4.12</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>32302345750</v>
+        <v>26476333065</v>
       </c>
       <c r="P15" t="n">
-        <v>1233000</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>120000</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>5000</v>
+        <v>70000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 과열 지정 및 연기금 7일 연속 매수. 릴레이 계약 공시 기대감 속 공매도 악마 비판.</t>
+          <t>공매도 및 대차 거래에 대한 우려와 주가 하락에 대한 불만. 주주들의 호소와 행동 촉구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '연기금', '계약 공시']</t>
+          <t>['공매도', '대차 거래', '주주 호소']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
         <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H16" t="n">
         <v>10.02</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>42093578625</v>
+        <v>42766989925</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16980</v>
+        <v>55400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.95</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="G17" t="n">
-        <v>362</v>
+        <v>495</v>
       </c>
       <c r="H17" t="n">
-        <v>3.97</v>
+        <v>1.32</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17940</v>
+        <v>58100</v>
       </c>
       <c r="K17" t="n">
-        <v>17770</v>
+        <v>63200</v>
       </c>
       <c r="L17" t="n">
-        <v>17940</v>
+        <v>63800</v>
       </c>
       <c r="M17" t="n">
-        <v>16900</v>
+        <v>53100</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>68849047945</v>
+        <v>47192073750</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>63800</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>25600</v>
       </c>
       <c r="R17" t="n">
-        <v>-168000</v>
+        <v>-170000</v>
       </c>
       <c r="S17" t="n">
-        <v>-15000</v>
+        <v>-21000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락에 따른 한국 시장 영향 우려. 주가 하락 및 외인 매도에 대한 불안감 증폭.</t>
+          <t>신약 허가 및 판매 호조에도 불구하고 주가 급락. 차명거래 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '주가 하락', '외인 매도']</t>
+          <t>['신약 허가', '주가 급락', '주가 조작']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54900</v>
+        <v>75900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.51%</t>
+          <t>'-5.71%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="F18" t="n">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="G18" t="n">
-        <v>486</v>
+        <v>820</v>
       </c>
       <c r="H18" t="n">
-        <v>1.32</v>
+        <v>22.49</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>58100</v>
+        <v>80500</v>
       </c>
       <c r="K18" t="n">
-        <v>63200</v>
+        <v>79600</v>
       </c>
       <c r="L18" t="n">
-        <v>63800</v>
+        <v>79600</v>
       </c>
       <c r="M18" t="n">
-        <v>53100</v>
+        <v>75700</v>
       </c>
       <c r="N18" t="n">
-        <v>1.3</v>
+        <v>22.59</v>
       </c>
       <c r="O18" t="n">
-        <v>46751931250</v>
+        <v>144577331800</v>
       </c>
       <c r="P18" t="n">
-        <v>63800</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>25600</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-170000</v>
+        <v>-360000</v>
       </c>
       <c r="S18" t="n">
-        <v>-21000</v>
+        <v>-54000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>신약 허가 및 판매 호조에도 불구하고 주가 급락. 차명거래 및 주가 조작 의혹 제기.</t>
+          <t>미국 가스 발전 확정 뉴스 언급. 원전 관련 부정적 전망과 공매도 관련 내용.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['신약 허가', '주가 급락', '주가 조작']</t>
+          <t>['가스 발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76050</v>
+        <v>16820</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.53%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E19" t="n">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="F19" t="n">
-        <v>171</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>792</v>
+        <v>379</v>
       </c>
       <c r="H19" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K19" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L19" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M19" t="n">
-        <v>75700</v>
+        <v>16800</v>
       </c>
       <c r="N19" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O19" t="n">
-        <v>141354289050</v>
+        <v>73555180860</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-360000</v>
+        <v>-168000</v>
       </c>
       <c r="S19" t="n">
-        <v>-54000</v>
+        <v>-15000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 가스 발전 확정 소식 속 원전 관련 부정적 전망. 공매도와 당국의 미흡한 대응에 대한 불만 고조.</t>
+          <t>미국 광통신주 하락에 따른 영향 우려. 주가 반등 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스 발전', '원전', '공매도']</t>
+          <t>['광통신', '주가 반등', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4855</v>
+        <v>7250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-7.29%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
-        <v>269</v>
+        <v>377</v>
       </c>
       <c r="H20" t="n">
-        <v>4.65</v>
+        <v>3.09</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5210</v>
+        <v>7820</v>
       </c>
       <c r="K20" t="n">
-        <v>5220</v>
+        <v>8080</v>
       </c>
       <c r="L20" t="n">
-        <v>5310</v>
+        <v>8510</v>
       </c>
       <c r="M20" t="n">
-        <v>4755</v>
+        <v>7170</v>
       </c>
       <c r="N20" t="n">
-        <v>4.72</v>
+        <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>58592989372</v>
+        <v>77384097310</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>23500</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>2890</v>
       </c>
       <c r="R20" t="n">
-        <v>-152000</v>
+        <v>-501000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 및 기타법인 대량 매도 악재 발생. 초대형 악재 속 주가 급락 및 투자자 경고.</t>
+          <t>본PF 대주단 구성 및 성수동 부동산 개발 관련 내용. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '대량 매도', '악재']</t>
+          <t>['본PF', '부동산 개발', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7240</v>
+        <v>4815</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.42%</t>
+          <t>'-7.58%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="H21" t="n">
-        <v>3.09</v>
+        <v>4.65</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7820</v>
+        <v>5210</v>
       </c>
       <c r="K21" t="n">
-        <v>8080</v>
+        <v>5220</v>
       </c>
       <c r="L21" t="n">
-        <v>8510</v>
+        <v>5310</v>
       </c>
       <c r="M21" t="n">
-        <v>7170</v>
+        <v>4755</v>
       </c>
       <c r="N21" t="n">
-        <v>5.12</v>
+        <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>76883719735</v>
+        <v>59554426801</v>
       </c>
       <c r="P21" t="n">
-        <v>23500</v>
+        <v>8100</v>
       </c>
       <c r="Q21" t="n">
-        <v>2890</v>
+        <v>592</v>
       </c>
       <c r="R21" t="n">
-        <v>-501000</v>
+        <v>-152000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 급락 및 공매도에 대한 비판. 성수동 부동산 개발 관련 기대감도 있으나, 전반적으로 부정적 전망 우세.</t>
+          <t>전환사채 및 기타법인 대량 매도 악재 발생. 초대형 악재 속 주가 급락 및 투자자 경고.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 급락', '공매도', '부동산 개발']</t>
+          <t>['전환사채', '대량 매도', '악재']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15240</v>
+        <v>15090</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.80%</t>
+          <t>'-9.69%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>29786085000</v>
+        <v>30181575770</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9980</v>
+        <v>9900</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.36%</t>
+          <t>'-10.08%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F23" t="n">
         <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>5902258540</v>
+        <v>6114020360</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_11.xlsx
+++ b/data/trending_integrated_20261008_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30679072390</v>
+        <v>30734562530</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14100</v>
+        <v>14110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.60%</t>
+          <t>'+17.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>37783725365</v>
+        <v>39238342120</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11300</v>
+        <v>11290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.37%</t>
+          <t>'+14.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>48832725445</v>
+        <v>49320921170</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13650</v>
+        <v>13730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.59%</t>
+          <t>'+9.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H5" t="n">
         <v>1.07</v>
@@ -886,7 +886,7 @@
         <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>70249511405</v>
+        <v>72419612405</v>
       </c>
       <c r="P5" t="n">
         <v>22250</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유증 물량 정리 및 바이오 관련 기대감. 1차 목표가 3만원 언급.</t>
+          <t>유증 물량 정리 완료 및 바이오스텝 강세 속 주가 상승 기대감 표출. HLB 승인 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유증', '바이오', '목표가']</t>
+          <t>['유증 물량', '바이오스텝', '주가 상승 기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6900</v>
+        <v>38700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.81%</t>
+          <t>'+6.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>167</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>19424509860</v>
+        <v>102948407275</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>199000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['기관', '외국인', '매수세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38600</v>
+        <v>6900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.63%</t>
+          <t>'+6.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
         <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>101105677325</v>
+        <v>19523786090</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R7" t="n">
-        <v>199000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '매수세']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4495</v>
+        <v>1745000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.19</v>
+        <v>-0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>418</v>
       </c>
       <c r="G8" t="n">
-        <v>142</v>
+        <v>1444</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46</v>
+        <v>49.59</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4430</v>
+        <v>1723000</v>
       </c>
       <c r="K8" t="n">
-        <v>4650</v>
+        <v>1722000</v>
       </c>
       <c r="L8" t="n">
-        <v>4855</v>
+        <v>1759000</v>
       </c>
       <c r="M8" t="n">
-        <v>4185</v>
+        <v>1722000</v>
       </c>
       <c r="N8" t="n">
-        <v>3.27</v>
+        <v>49.71</v>
       </c>
       <c r="O8" t="n">
-        <v>76260761607</v>
+        <v>2106181416000</v>
       </c>
       <c r="P8" t="n">
-        <v>5470</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>2810</v>
+        <v>403000</v>
       </c>
       <c r="R8" t="n">
-        <v>-469000</v>
+        <v>-25000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 200% 폭등 및 WHO 페스트 관련 뉴스 속보. 다만, 전염병 확산은 제한적이며, 주가 흐름은 미미함.</t>
+          <t>솔리다임 상장 관련 논란 속 주가 상승 기대감과 외인 매수세 언급. 정부 정책 비판도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미국 항생제', '페스트', 'WHO']</t>
+          <t>['솔리다임', '외인 매수세', '주가 상승 기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1745500</v>
+        <v>4480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.12</v>
+        <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>417</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>1583</v>
+        <v>141</v>
       </c>
       <c r="H9" t="n">
-        <v>49.59</v>
+        <v>4.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1723000</v>
+        <v>4430</v>
       </c>
       <c r="K9" t="n">
-        <v>1722000</v>
+        <v>4650</v>
       </c>
       <c r="L9" t="n">
-        <v>1759000</v>
+        <v>4855</v>
       </c>
       <c r="M9" t="n">
-        <v>1722000</v>
+        <v>4185</v>
       </c>
       <c r="N9" t="n">
-        <v>49.71</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>2043934886500</v>
+        <v>77546061777</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>5470</v>
       </c>
       <c r="Q9" t="n">
-        <v>403000</v>
+        <v>2810</v>
       </c>
       <c r="R9" t="n">
-        <v>-25000</v>
+        <v>-469000</v>
       </c>
       <c r="S9" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란. 마이크론 급등 및 삼성전자 실적 발표에 따른 영향 분석.</t>
+          <t>미국 항생제 보유 회사 주가 200% 폭등 및 WHO 페스트 관련 뉴스 속보. 다만, 전염병 확산은 제한적이며, 주가 흐름은 미미함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '마이크론', '실적 발표']</t>
+          <t>['미국 항생제', '페스트', 'WHO']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>10639298980</v>
+        <v>10913236015</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45900</v>
+        <v>46000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
-        <v>755</v>
+        <v>839</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>24282898550</v>
+        <v>25140039400</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 및 글로벌 3상 종료 약물 관련 긍정적 전망. 공매도 압박.</t>
+          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 공방 속 주가 상승 전망. 우상향 차트 시작 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '3상 임상', '공매도']</t>
+          <t>['리보세라닙', '공매도', '주가 상승 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>266750</v>
+        <v>266500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G12" t="n">
-        <v>1821</v>
+        <v>1848</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>1893876816500</v>
+        <v>2023395268000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>영업이익 107조에도 주가 부양 실패. 정치적 책임론 제기.</t>
+          <t>107조 영업이익에도 주가 부양 안 되는 상황에 대한 불만 표출. 시장 시스템 붕괴 및 특정 정치인 책임론 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '정치']</t>
+          <t>['영업이익', '주가 부양', '정치인 책임론']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>234000</v>
+        <v>236000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="H13" t="n">
         <v>3.47</v>
@@ -1622,7 +1622,7 @@
         <v>4.12</v>
       </c>
       <c r="O13" t="n">
-        <v>32841520250</v>
+        <v>33350710750</v>
       </c>
       <c r="P13" t="n">
         <v>1233000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18970</v>
+        <v>18960</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>29687693930</v>
+        <v>30488443185</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
+          <t>증권사 애널리스트 및 리딩방에 대한 불신, 주주환원 정책 부재 및 52주 신저점 경신에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '신저가', '애널리스트']</t>
+          <t>['애널리스트 불신', '주주환원', '52주 신저점']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1774,13 +1774,13 @@
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>26476333065</v>
+        <v>27086998550</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28550</v>
+        <v>28650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.19%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H16" t="n">
         <v>10.02</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>42766989925</v>
+        <v>43462074825</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55400</v>
+        <v>75800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-5.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G17" t="n">
-        <v>495</v>
+        <v>850</v>
       </c>
       <c r="H17" t="n">
-        <v>1.32</v>
+        <v>22.49</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>58100</v>
+        <v>80500</v>
       </c>
       <c r="K17" t="n">
-        <v>63200</v>
+        <v>79600</v>
       </c>
       <c r="L17" t="n">
-        <v>63800</v>
+        <v>79600</v>
       </c>
       <c r="M17" t="n">
-        <v>53100</v>
+        <v>75700</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>22.59</v>
       </c>
       <c r="O17" t="n">
-        <v>47192073750</v>
+        <v>149058944100</v>
       </c>
       <c r="P17" t="n">
-        <v>63800</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>25600</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-170000</v>
+        <v>-360000</v>
       </c>
       <c r="S17" t="n">
-        <v>-21000</v>
+        <v>-54000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>신약 허가 및 판매 호조에도 불구하고 주가 급락. 차명거래 및 주가 조작 의혹 제기.</t>
+          <t>미국 텍사스 가스 발전 확정 속보와 함께 원전 관련 긍정적 언급. 그러나 주가 하락 및 공매도에 대한 불만 지속.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신약 허가', '주가 급락', '주가 조작']</t>
+          <t>['가스 발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75900</v>
+        <v>16860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.71%</t>
+          <t>'-6.02%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>820</v>
+        <v>403</v>
       </c>
       <c r="H18" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K18" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L18" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M18" t="n">
-        <v>75700</v>
+        <v>16800</v>
       </c>
       <c r="N18" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>144577331800</v>
+        <v>75673791700</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-360000</v>
+        <v>-168000</v>
       </c>
       <c r="S18" t="n">
-        <v>-54000</v>
+        <v>-15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 가스 발전 확정 뉴스 언급. 원전 관련 부정적 전망과 공매도 관련 내용.</t>
+          <t>미국 광통신주 하락 영향 속 주가 부진. 외인 매도 및 프로그램 매매에 대한 불안감 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['가스 발전', '원전', '공매도']</t>
+          <t>['광통신주', '외인 매도', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16820</v>
+        <v>54600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-6.02%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.95</v>
+        <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="G19" t="n">
-        <v>379</v>
+        <v>515</v>
       </c>
       <c r="H19" t="n">
-        <v>3.97</v>
+        <v>1.32</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17940</v>
+        <v>58100</v>
       </c>
       <c r="K19" t="n">
-        <v>17770</v>
+        <v>63200</v>
       </c>
       <c r="L19" t="n">
-        <v>17940</v>
+        <v>63800</v>
       </c>
       <c r="M19" t="n">
-        <v>16800</v>
+        <v>53100</v>
       </c>
       <c r="N19" t="n">
-        <v>4.92</v>
+        <v>1.3</v>
       </c>
       <c r="O19" t="n">
-        <v>73555180860</v>
+        <v>47749894100</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>63800</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>25600</v>
       </c>
       <c r="R19" t="n">
-        <v>-168000</v>
+        <v>-170000</v>
       </c>
       <c r="S19" t="n">
-        <v>-15000</v>
+        <v>-21000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락에 따른 영향 우려. 주가 반등 및 공매도 관련 언급.</t>
+          <t>신약 허가 및 판매 호조에도 불구하고 급락하는 주가에 대한 의문 제기. 주가 조작 및 공매도 의심.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '주가 반등', '공매도']</t>
+          <t>['신약 허가', '급락', '주가 조작 의심']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7250</v>
+        <v>7330</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.29%</t>
+          <t>'-6.27%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G20" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="H20" t="n">
         <v>3.09</v>
@@ -2266,7 +2266,7 @@
         <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>77384097310</v>
+        <v>77711867925</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2326,13 +2326,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>59554426801</v>
+        <v>60339913228</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 및 기타법인 대량 매도 악재 발생. 초대형 악재 속 주가 급락 및 투자자 경고.</t>
+          <t>전환사채 발행 및 대규모 기타법인 매도에 따른 악재 발생. 장기 전망 긍정적 언급도 있으나 단기 하락 우려.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '대량 매도', '악재']</t>
+          <t>['전환사채', '기타법인 매도', '단기 하락 우려']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15090</v>
+        <v>15200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.69%</t>
+          <t>'-9.04%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>30181575770</v>
+        <v>30743475085</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9900</v>
+        <v>9910</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.08%</t>
+          <t>'-9.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>6114020360</v>
+        <v>6255591450</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 급등 및 케냐 에볼라 확진 소식에 따른 기대감. 그러나 과거 패턴 언급 및 주가 하락 지속.</t>
+          <t>미국 항생제 관련주 폭등 속 신풍제약 주가 부진. 바이러스 대장주로서의 기대감과 함께 주가 장난질에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['항생제', '에볼라', '주가하락']</t>
+          <t>['항생제 관련주', '주가 부진', '바이러스 대장주']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated_20261008_11.xlsx
+++ b/data/trending_integrated_20261008_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30734562530</v>
+        <v>30820731890</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -619,7 +619,7 @@
         <v>1086</v>
       </c>
       <c r="R2" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14110</v>
+        <v>14150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.68%</t>
+          <t>'+18.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>40</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>39238342120</v>
+        <v>40033361180</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11290</v>
+        <v>11240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.27%</t>
+          <t>'+13.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>49320921170</v>
+        <v>50086187750</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13730</v>
+        <v>13400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.23%</t>
+          <t>'+6.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
         <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H5" t="n">
         <v>1.07</v>
@@ -886,7 +886,7 @@
         <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>72419612405</v>
+        <v>74325565220</v>
       </c>
       <c r="P5" t="n">
         <v>22250</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유증 물량 정리 완료 및 바이오스텝 강세 속 주가 상승 기대감 표출. HLB 승인 시 추가 상승 전망.</t>
+          <t>HLB제약, 바이오스텝 관련 언급과 함께 1차 목표가 3만원 제시. 유증 물량 소화 및 추가 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유증 물량', '바이오스텝', '주가 상승 기대']</t>
+          <t>['바이오스텝', '유증 물량', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38700</v>
+        <v>38500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.91%</t>
+          <t>'+6.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H6" t="n">
         <v>31.86</v>
@@ -978,7 +978,7 @@
         <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>102948407275</v>
+        <v>104805260900</v>
       </c>
       <c r="P6" t="n">
         <v>45000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6900</v>
+        <v>6850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.81%</t>
+          <t>'+6.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>19523786090</v>
+        <v>19610351780</v>
       </c>
       <c r="P7" t="n">
         <v>9680</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1745000</v>
+        <v>4515</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.12</v>
+        <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>418</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>1444</v>
+        <v>144</v>
       </c>
       <c r="H8" t="n">
-        <v>49.59</v>
+        <v>4.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1723000</v>
+        <v>4430</v>
       </c>
       <c r="K8" t="n">
-        <v>1722000</v>
+        <v>4650</v>
       </c>
       <c r="L8" t="n">
-        <v>1759000</v>
+        <v>4855</v>
       </c>
       <c r="M8" t="n">
-        <v>1722000</v>
+        <v>4185</v>
       </c>
       <c r="N8" t="n">
-        <v>49.71</v>
+        <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>2106181416000</v>
+        <v>79716070807</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>5470</v>
       </c>
       <c r="Q8" t="n">
-        <v>403000</v>
+        <v>2810</v>
       </c>
       <c r="R8" t="n">
-        <v>-25000</v>
+        <v>-469000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란 속 주가 상승 기대감과 외인 매수세 언급. 정부 정책 비판도 존재.</t>
+          <t>국제약품, 미국 항생제 회사 주가 폭등 및 WHO 관련 뉴스에 대한 기대감. 하지만 구체적인 사업 연관성이나 팩트 기반 분석은 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '외인 매수세', '주가 상승 기대']</t>
+          <t>['항생제', 'WHO', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4480</v>
+        <v>1739500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.19</v>
+        <v>-0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>423</v>
       </c>
       <c r="G9" t="n">
-        <v>141</v>
+        <v>1444</v>
       </c>
       <c r="H9" t="n">
-        <v>4.46</v>
+        <v>49.59</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4430</v>
+        <v>1723000</v>
       </c>
       <c r="K9" t="n">
-        <v>4650</v>
+        <v>1722000</v>
       </c>
       <c r="L9" t="n">
-        <v>4855</v>
+        <v>1759000</v>
       </c>
       <c r="M9" t="n">
-        <v>4185</v>
+        <v>1722000</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>49.71</v>
       </c>
       <c r="O9" t="n">
-        <v>77546061777</v>
+        <v>2164569179500</v>
       </c>
       <c r="P9" t="n">
-        <v>5470</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>2810</v>
+        <v>403000</v>
       </c>
       <c r="R9" t="n">
-        <v>-469000</v>
+        <v>-25000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 200% 폭등 및 WHO 페스트 관련 뉴스 속보. 다만, 전염병 확산은 제한적이며, 주가 흐름은 미미함.</t>
+          <t>SK하이닉스, 솔리다임 상장 이슈 관련 언급. 자사주 매입 및 외인 매매 동향 주시. 일부 긍정적 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미국 항생제', '페스트', 'WHO']</t>
+          <t>['솔리다임', '자사주 매입', '외인 동향']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8280</v>
+        <v>8250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>10913236015</v>
+        <v>11288413485</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46000</v>
+        <v>45850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F11" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G11" t="n">
-        <v>839</v>
+        <v>895</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>25140039400</v>
+        <v>25952675850</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 공방 속 주가 상승 전망. 우상향 차트 시작 분석.</t>
+          <t>HLB, 리보세라닙 병용요법 허가 기대감 속에서 공매도와의 관계 언급. 긍정적 차트 분석 및 우상향 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '주가 상승 전망']</t>
+          <t>['리보세라닙', '공매도', '우상향']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>266500</v>
+        <v>266000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G12" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>2023395268000</v>
+        <v>2094309301000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>107조 영업이익에도 주가 부양 안 되는 상황에 대한 불만 표출. 시장 시스템 붕괴 및 특정 정치인 책임론 제기.</t>
+          <t>삼성전자, 107조 영업이익에도 주가 부양 실패에 대한 불만 고조. 시스템 및 정치적 요인 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '정치인 책임론']</t>
+          <t>['영업이익', '주가 부양', '시장 시스템']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1596,7 +1596,7 @@
         <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>611</v>
+        <v>651</v>
       </c>
       <c r="H13" t="n">
         <v>3.47</v>
@@ -1622,7 +1622,7 @@
         <v>4.12</v>
       </c>
       <c r="O13" t="n">
-        <v>33350710750</v>
+        <v>34146362250</v>
       </c>
       <c r="P13" t="n">
         <v>1233000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아일리아 영업이익 및 릴레이 계약 공시. 공매도 금지 및 연기금 매수 동향.</t>
+          <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아일리아', '계약 공시', '공매도 금지']</t>
+          <t>['아일리아', '연기금', '계약공시']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18960</v>
+        <v>18950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1708,13 +1708,13 @@
         <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>18950</v>
+        <v>18940</v>
       </c>
       <c r="N14" t="n">
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>30488443185</v>
+        <v>31410144980</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 및 리딩방에 대한 불신, 주주환원 정책 부재 및 52주 신저점 경신에 대한 우려 제기.</t>
+          <t>삼성중공업, 5달간 주가 하락에 대한 불안감과 조선주 전반에 대한 부정적 전망. 증권사 애널리스트 및 리딩방 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['애널리스트 불신', '주주환원', '52주 신저점']</t>
+          <t>['조선주', '신저점', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16800</v>
+        <v>16810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
         <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>27086998550</v>
+        <v>27737253295</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28650</v>
+        <v>28500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.86%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
         <v>133</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>43462074825</v>
+        <v>44755890125</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75800</v>
+        <v>16920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.84%</t>
+          <t>'-5.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>850</v>
+        <v>424</v>
       </c>
       <c r="H17" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>75700</v>
+        <v>16800</v>
       </c>
       <c r="N17" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>149058944100</v>
+        <v>77138001655</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-360000</v>
+        <v>-168000</v>
       </c>
       <c r="S17" t="n">
-        <v>-54000</v>
+        <v>-15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스 발전 확정 속보와 함께 원전 관련 긍정적 언급. 그러나 주가 하락 및 공매도에 대한 불만 지속.</t>
+          <t>미국 광통신주 하락 영향 속 주가 부진. 외인 매도 및 프로그램 매매에 대한 불안감 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['가스 발전', '원전', '공매도']</t>
+          <t>['광통신주', '외인 매도', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16860</v>
+        <v>75800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.02%</t>
+          <t>'-5.84%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>314</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="G18" t="n">
-        <v>403</v>
+        <v>864</v>
       </c>
       <c r="H18" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K18" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L18" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M18" t="n">
-        <v>16800</v>
+        <v>75700</v>
       </c>
       <c r="N18" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O18" t="n">
-        <v>75673791700</v>
+        <v>151488241250</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-168000</v>
+        <v>-360000</v>
       </c>
       <c r="S18" t="n">
-        <v>-15000</v>
+        <v>-54000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 속 주가 부진. 외인 매도 및 프로그램 매매에 대한 불안감 표출.</t>
+          <t>두산에너빌리티, 한미 텍사스 가스발전 확정 및 원전 관련 뉴스 언급. 하지만 주가 하락에 대한 불만과 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신주', '외인 매도', '프로그램 매매']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54600</v>
+        <v>7300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.02%</t>
+          <t>'-6.65%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>-2.03</v>
       </c>
       <c r="E19" t="n">
-        <v>271</v>
+        <v>152</v>
       </c>
       <c r="F19" t="n">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>515</v>
+        <v>411</v>
       </c>
       <c r="H19" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>58100</v>
+        <v>7820</v>
       </c>
       <c r="K19" t="n">
-        <v>63200</v>
+        <v>8080</v>
       </c>
       <c r="L19" t="n">
-        <v>63800</v>
+        <v>8510</v>
       </c>
       <c r="M19" t="n">
-        <v>53100</v>
+        <v>7170</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3</v>
+        <v>5.12</v>
       </c>
       <c r="O19" t="n">
-        <v>47749894100</v>
+        <v>78078435610</v>
       </c>
       <c r="P19" t="n">
-        <v>63800</v>
+        <v>23500</v>
       </c>
       <c r="Q19" t="n">
-        <v>25600</v>
+        <v>2890</v>
       </c>
       <c r="R19" t="n">
-        <v>-170000</v>
+        <v>-501000</v>
       </c>
       <c r="S19" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>신약 허가 및 판매 호조에도 불구하고 급락하는 주가에 대한 의문 제기. 주가 조작 및 공매도 의심.</t>
+          <t>삼표시멘트, 3-4조 규모 본PF 및 부동산주 관련 언급. 하지만 주가 하락 및 개인 투자자 매도에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['신약 허가', '급락', '주가 조작 의심']</t>
+          <t>['본PF', '부동산주', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7330</v>
+        <v>4845</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.27%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>392</v>
+        <v>293</v>
       </c>
       <c r="H20" t="n">
-        <v>3.09</v>
+        <v>4.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7820</v>
+        <v>5210</v>
       </c>
       <c r="K20" t="n">
-        <v>8080</v>
+        <v>5220</v>
       </c>
       <c r="L20" t="n">
-        <v>8510</v>
+        <v>5310</v>
       </c>
       <c r="M20" t="n">
-        <v>7170</v>
+        <v>4755</v>
       </c>
       <c r="N20" t="n">
-        <v>5.12</v>
+        <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>77711867925</v>
+        <v>60950745770</v>
       </c>
       <c r="P20" t="n">
-        <v>23500</v>
+        <v>8100</v>
       </c>
       <c r="Q20" t="n">
-        <v>2890</v>
+        <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-501000</v>
+        <v>-152000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 및 성수동 부동산 개발 관련 내용. 공매도 관련 언급.</t>
+          <t>전환사채 발행 및 대규모 기타법인 매도에 따른 악재 발생. 장기 전망 긍정적 언급도 있으나 단기 하락 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['본PF', '부동산 개발', '공매도']</t>
+          <t>['전환사채', '기타법인 매도', '단기 하락 우려']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4815</v>
+        <v>53900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.58%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>274</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="G21" t="n">
-        <v>282</v>
+        <v>539</v>
       </c>
       <c r="H21" t="n">
-        <v>4.65</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5210</v>
+        <v>58100</v>
       </c>
       <c r="K21" t="n">
-        <v>5220</v>
+        <v>63200</v>
       </c>
       <c r="L21" t="n">
-        <v>5310</v>
+        <v>63800</v>
       </c>
       <c r="M21" t="n">
-        <v>4755</v>
+        <v>53100</v>
       </c>
       <c r="N21" t="n">
-        <v>4.72</v>
+        <v>1.3</v>
       </c>
       <c r="O21" t="n">
-        <v>60339913228</v>
+        <v>48549441700</v>
       </c>
       <c r="P21" t="n">
-        <v>8100</v>
+        <v>63800</v>
       </c>
       <c r="Q21" t="n">
-        <v>592</v>
+        <v>25600</v>
       </c>
       <c r="R21" t="n">
-        <v>-152000</v>
+        <v>-170000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 대규모 기타법인 매도에 따른 악재 발생. 장기 전망 긍정적 언급도 있으나 단기 하락 우려.</t>
+          <t>한미사이언스, 신약 허가 및 신제품 판매 호조에도 불구하고 급락에 대한 의문 제기. 주가 조작 및 공매도 의혹.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '기타법인 매도', '단기 하락 우려']</t>
+          <t>['신약 허가', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15200</v>
+        <v>15080</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.04%</t>
+          <t>'-9.75%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>30743475085</v>
+        <v>31191466730</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2510,13 +2510,13 @@
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>6255591450</v>
+        <v>6313838320</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>
